--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -1245,7 +1245,7 @@
           <t>- | 2363呎 (4+房)
 $8364万
 $35,396/呎
-(16年-01月)</t>
+(16年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
           <t>- | 2406呎 (4+房)
 $8439万
 $35,075/呎
-(16年-01月)</t>
+(16年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
           <t>- | 2406呎 (4+房)
 $9638万
 $40,058/呎
-(14年-08月)</t>
+(14年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
           <t>- | 2433呎 (4+房)
 $8924万
 $36,681/呎
-(17年-06月)</t>
+(17年-06月-13日)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1410,7 @@
           <t>- | 3109呎 (4+房)
 $15066万
 $48,459/呎
-(15年-02月)</t>
+(15年-02月-12日)</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
           <t>- | 1506呎 (3房)
 $4951万
 $32,878/呎
-(15年-02月)</t>
+(15年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
           <t>- | 1506呎 (3房)
 $5065万
 $33,634/呎
-(15年-03月)</t>
+(15年-03月-29日)</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
           <t>- | 3039呎 (4+房)
 $15000万
 $49,358/呎
-(15年-06月)</t>
+(15年-06月-12日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -199,61 +199,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -626,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -639,6 +639,10 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -696,6 +700,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -742,6 +766,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>341780000</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>67733</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>(A1)現金或即時按揭付款</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -777,7 +817,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2016-01-11</t>
+          <t>2016-01-12</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -788,6 +828,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>83641800</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>35396</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -823,7 +879,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2016-01-14</t>
+          <t>2016-01-15</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -834,6 +890,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>84390000</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>35075</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -869,7 +941,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2014-08-20</t>
+          <t>2014-08-21</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -880,6 +952,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>96380000</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>40058</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -915,7 +1003,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2017-06-13</t>
+          <t>2017-06-14</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -926,6 +1014,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>89244600</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>36681</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -961,7 +1065,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2015-02-12</t>
+          <t>2015-02-13</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -972,6 +1076,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>150659200</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>48459</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1007,7 +1127,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2015-02-02</t>
+          <t>2015-02-03</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1018,6 +1138,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>49514400</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>32878</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1053,7 +1189,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2015-03-29</t>
+          <t>2015-03-30</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1064,6 +1200,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>50652880</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>33634</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1099,7 +1251,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2015-06-12</t>
+          <t>2015-06-13</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1110,13 +1262,29 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>49358</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1245,7 +1413,7 @@
           <t>- | 2363呎 (4+房)
 $8364万
 $35,396/呎
-(16年-01月-11日)</t>
+(16年-01月-12日)</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1428,7 @@
           <t>- | 2406呎 (4+房)
 $8439万
 $35,075/呎
-(16年-01月-14日)</t>
+(16年-01月-15日)</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1443,7 @@
           <t>- | 2406呎 (4+房)
 $9638万
 $40,058/呎
-(14年-08月-20日)</t>
+(14年-08月-21日)</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1458,7 @@
           <t>- | 2433呎 (4+房)
 $8924万
 $36,681/呎
-(17年-06月-13日)</t>
+(17年-06月-14日)</t>
         </is>
       </c>
     </row>
@@ -1410,7 +1578,7 @@
           <t>- | 3109呎 (4+房)
 $15066万
 $48,459/呎
-(15年-02月-12日)</t>
+(15年-02月-13日)</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1593,7 @@
           <t>- | 1506呎 (3房)
 $4951万
 $32,878/呎
-(15年-02月-02日)</t>
+(15年-02月-03日)</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1608,7 @@
           <t>- | 1506呎 (3房)
 $5065万
 $33,634/呎
-(15年-03月-29日)</t>
+(15年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1623,7 @@
           <t>- | 3039呎 (4+房)
 $15000万
 $49,358/呎
-(15年-06月-12日)</t>
+(15年-06月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -9,7 +9,6 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -199,61 +198,61 @@
   <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -626,7 +625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -639,10 +638,6 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -700,26 +695,6 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>最高折扣</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>折实总价 (港币)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>折实呎价 (港币/呎)</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>付款办法</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -766,22 +741,6 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
-        </is>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>341780000</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>67733</v>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>(A1)現金或即時按揭付款</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -817,7 +776,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2016-01-12</t>
+          <t>2016-01-11</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -828,22 +787,6 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>83641800</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>35396</v>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -879,7 +822,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2016-01-15</t>
+          <t>2016-01-14</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -890,22 +833,6 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>84390000</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>35075</v>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -941,7 +868,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2014-08-21</t>
+          <t>2014-08-20</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -952,22 +879,6 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K6" s="5" t="n">
-        <v>96380000</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>40058</v>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
@@ -1003,7 +914,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2017-06-14</t>
+          <t>2017-06-13</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1014,277 +925,13 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K7" s="5" t="n">
-        <v>89244600</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>36681</v>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>B座</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>3109</v>
-      </c>
-      <c r="F8" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>2015-02-13</t>
-        </is>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>150659200</v>
-      </c>
-      <c r="I8" s="5" t="n">
-        <v>48459</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>150659200</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>48459</v>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>B座</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>2015-02-03</t>
-        </is>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>49514400</v>
-      </c>
-      <c r="I9" s="5" t="n">
-        <v>32878</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>49514400</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>32878</v>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>B座</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>3房</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>2015-03-30</t>
-        </is>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>50652880</v>
-      </c>
-      <c r="I10" s="5" t="n">
-        <v>33634</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>50652880</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>33634</v>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>B座</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>4+房</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>3039</v>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>已售</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>2015-06-13</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="I11" s="5" t="n">
-        <v>49358</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="n">
-        <v>150000000</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>49358</v>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -1413,7 +1060,7 @@
           <t>- | 2363呎 (4+房)
 $8364万
 $35,396/呎
-(16年-01月-12日)</t>
+(16年-01月-11日)</t>
         </is>
       </c>
     </row>
@@ -1428,7 +1075,7 @@
           <t>- | 2406呎 (4+房)
 $8439万
 $35,075/呎
-(16年-01月-15日)</t>
+(16年-01月-14日)</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1090,7 @@
           <t>- | 2406呎 (4+房)
 $9638万
 $40,058/呎
-(14年-08月-21日)</t>
+(14年-08月-20日)</t>
         </is>
       </c>
     </row>
@@ -1458,172 +1105,7 @@
           <t>- | 2433呎 (4+房)
 $8924万
 $36,681/呎
-(17年-06月-14日)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>B座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="9" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="10" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="11" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B3" s="14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="19" t="inlineStr">
-        <is>
-          <t>楼层</t>
-        </is>
-      </c>
-      <c r="B4" s="19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="58" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>5&amp;6</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t>- | 3109呎 (4+房)
-$15066万
-$48,459/呎
-(15年-02月-13日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="58" customHeight="1">
-      <c r="A6" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B6" s="21" t="inlineStr">
-        <is>
-          <t>- | 1506呎 (3房)
-$4951万
-$32,878/呎
-(15年-02月-03日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="58" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B7" s="21" t="inlineStr">
-        <is>
-          <t>- | 1506呎 (3房)
-$5065万
-$33,634/呎
-(15年-03月-30日)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="58" customHeight="1">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>1&amp;2</t>
-        </is>
-      </c>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t>- | 3039呎 (4+房)
-$15000万
-$49,358/呎
-(15年-06月-13日)</t>
+(17年-06月-13日)</t>
         </is>
       </c>
     </row>

--- a/files/港岛-跑马地-339 Tai Hang Road.xlsx
+++ b/files/港岛-跑马地-339 Tai Hang Road.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="A座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B座" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -625,7 +626,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -924,6 +925,190 @@
         <v>36681</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>B座</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3109</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>150659200</v>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>48459</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>B座</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>2015-02-02</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>49514400</v>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>32878</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>B座</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>3房</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>2015-03-29</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>50652880</v>
+      </c>
+      <c r="I10" s="5" t="n">
+        <v>33634</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>B座</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>4+房</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>3039</v>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>已售</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2015-06-12</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>150000000</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>49358</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
         <is>
           <t>否</t>
         </is>
@@ -1116,4 +1301,169 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>B座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>5&amp;6</t>
+        </is>
+      </c>
+      <c r="B5" s="21" t="inlineStr">
+        <is>
+          <t>- | 3109呎 (4+房)
+$15066万
+$48,459/呎
+(15年-02月-12日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B6" s="21" t="inlineStr">
+        <is>
+          <t>- | 1506呎 (3房)
+$4951万
+$32,878/呎
+(15年-02月-02日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>- | 1506呎 (3房)
+$5065万
+$33,634/呎
+(15年-03月-29日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>1&amp;2</t>
+        </is>
+      </c>
+      <c r="B8" s="21" t="inlineStr">
+        <is>
+          <t>- | 3039呎 (4+房)
+$15000万
+$49,358/呎
+(15年-06月-12日)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>